--- a/REVISÃO 3.xlsx
+++ b/REVISÃO 3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Fatec\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4154FFF5-8BE6-497A-A332-32067D6FBBA4}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C56A541F-19CF-417B-8DC1-2AC3D91C452F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" xr2:uid="{5228A228-0407-4908-8096-B64EA880E55B}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="7890" xr2:uid="{C97C509E-2113-47C8-9968-9A8307FD41EC}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -27,52 +27,52 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
-    <t>N°</t>
+    <t>Nº</t>
   </si>
   <si>
     <t>NOME</t>
   </si>
   <si>
-    <t>SALÁRIO HBRUTO</t>
+    <t>Salário Bruto</t>
   </si>
   <si>
     <t>INSS</t>
   </si>
   <si>
-    <t>GRATIFICAÇÃO</t>
+    <t>Gratificação</t>
   </si>
   <si>
     <t>INSS R$</t>
   </si>
   <si>
-    <t>GRATIFICAÇÃO R$</t>
-  </si>
-  <si>
-    <t>SALÁRIO LÍQUIDO</t>
-  </si>
-  <si>
-    <t>EDUARDO</t>
-  </si>
-  <si>
-    <t>MARIA</t>
-  </si>
-  <si>
-    <t>HELENA</t>
-  </si>
-  <si>
-    <t>GABRIELA</t>
-  </si>
-  <si>
-    <t>EDSON</t>
-  </si>
-  <si>
-    <t>ELISANGELA</t>
-  </si>
-  <si>
-    <t>REGINA</t>
-  </si>
-  <si>
-    <t>PAULO</t>
+    <t>Gratificação R$</t>
+  </si>
+  <si>
+    <t>Salário Líquido</t>
+  </si>
+  <si>
+    <t>Eduardo</t>
+  </si>
+  <si>
+    <t>Maria</t>
+  </si>
+  <si>
+    <t>Helena</t>
+  </si>
+  <si>
+    <t>Gabriela</t>
+  </si>
+  <si>
+    <t>Edson</t>
+  </si>
+  <si>
+    <t>Elisangela</t>
+  </si>
+  <si>
+    <t>Regina</t>
+  </si>
+  <si>
+    <t>Paulo</t>
   </si>
 </sst>
 </file>
@@ -106,12 +106,27 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -120,11 +135,15 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moeda" xfId="1" builtinId="4"/>
@@ -440,272 +459,274 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE14B7B3-1105-4C7A-8B00-AF50DD7F3DC1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93F46740-14D5-4D1F-BCF1-893D293DEBDE}">
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="11.28515625" customWidth="1"/>
-    <col min="3" max="3" width="17" customWidth="1"/>
-    <col min="5" max="5" width="13.5703125" customWidth="1"/>
-    <col min="6" max="6" width="9.85546875" customWidth="1"/>
-    <col min="7" max="8" width="17.140625" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="13.85546875" customWidth="1"/>
+    <col min="4" max="4" width="10.5703125" customWidth="1"/>
+    <col min="5" max="5" width="11.7109375" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" customWidth="1"/>
+    <col min="8" max="8" width="13.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2">
+      <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2" s="3">
         <v>853</v>
       </c>
-      <c r="D2" s="1">
+      <c r="D2" s="4">
         <v>0.1</v>
       </c>
-      <c r="E2" s="1">
+      <c r="E2" s="5">
         <v>0.09</v>
       </c>
       <c r="F2" s="3">
-        <f>C2*D2</f>
+        <f>SUM(C2*D2)</f>
         <v>85.300000000000011</v>
       </c>
       <c r="G2" s="3">
-        <f>C2*E2</f>
+        <f>SUM(C2*E2)</f>
         <v>76.77</v>
       </c>
       <c r="H2" s="3">
-        <f>C2+G2-F2</f>
+        <f>SUM(C2+G2-F2)</f>
         <v>844.47</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3">
+      <c r="A3" s="2">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="3">
         <v>951</v>
       </c>
-      <c r="D3" s="1">
+      <c r="D3" s="4">
         <v>9.9900000000000003E-2</v>
       </c>
-      <c r="E3" s="1">
+      <c r="E3" s="5">
         <v>0.08</v>
       </c>
       <c r="F3" s="3">
-        <f t="shared" ref="F3:F9" si="0">C3*D3</f>
+        <f>SUM(C3*D3)</f>
         <v>95.004900000000006</v>
       </c>
       <c r="G3" s="3">
-        <f t="shared" ref="G3:G9" si="1">C3*E3</f>
+        <f t="shared" ref="G3:G9" si="0">SUM(C3*E3)</f>
         <v>76.08</v>
       </c>
       <c r="H3" s="3">
-        <f t="shared" ref="H3:H9" si="2">C3+G3-F3</f>
+        <f t="shared" ref="H3:H9" si="1">SUM(C3+G3-F3)</f>
         <v>932.07509999999991</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4">
+      <c r="A4" s="2">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="3">
         <v>456</v>
       </c>
-      <c r="D4" s="1">
+      <c r="D4" s="4">
         <v>8.6400000000000005E-2</v>
       </c>
-      <c r="E4" s="1">
+      <c r="E4" s="5">
         <v>0.06</v>
       </c>
       <c r="F4" s="3">
+        <f>SUM(C4*D4)</f>
+        <v>39.398400000000002</v>
+      </c>
+      <c r="G4" s="3">
         <f t="shared" si="0"/>
-        <v>39.398400000000002</v>
-      </c>
-      <c r="G4" s="3">
+        <v>27.36</v>
+      </c>
+      <c r="H4" s="3">
         <f t="shared" si="1"/>
-        <v>27.36</v>
-      </c>
-      <c r="H4" s="3">
+        <v>443.96160000000003</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="3">
+        <v>500</v>
+      </c>
+      <c r="D5" s="4">
+        <v>8.5000000000000006E-2</v>
+      </c>
+      <c r="E5" s="5">
+        <v>0.06</v>
+      </c>
+      <c r="F5" s="3">
+        <f>SUM(C5*D5)</f>
+        <v>42.5</v>
+      </c>
+      <c r="G5" s="3">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="H5" s="3">
+        <f t="shared" si="1"/>
+        <v>487.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="3">
+        <v>850</v>
+      </c>
+      <c r="D6" s="4">
+        <v>8.9899999999999994E-2</v>
+      </c>
+      <c r="E6" s="5">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="F6" s="3">
+        <f>SUM(C6*D6)</f>
+        <v>76.414999999999992</v>
+      </c>
+      <c r="G6" s="3">
+        <f t="shared" si="0"/>
+        <v>59.500000000000007</v>
+      </c>
+      <c r="H6" s="3">
+        <f t="shared" si="1"/>
+        <v>833.08500000000004</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="3">
+        <v>459</v>
+      </c>
+      <c r="D7" s="4">
+        <v>6.25E-2</v>
+      </c>
+      <c r="E7" s="5">
+        <v>0.05</v>
+      </c>
+      <c r="F7" s="3">
+        <f>SUM(C7*D7)</f>
+        <v>28.6875</v>
+      </c>
+      <c r="G7" s="3">
+        <f t="shared" si="0"/>
+        <v>22.950000000000003</v>
+      </c>
+      <c r="H7" s="3">
+        <f t="shared" si="1"/>
+        <v>453.26249999999999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" s="3">
+        <v>478</v>
+      </c>
+      <c r="D8" s="4">
+        <v>7.1199999999999999E-2</v>
+      </c>
+      <c r="E8" s="5">
+        <v>0.05</v>
+      </c>
+      <c r="F8" s="3">
+        <f t="shared" ref="F3:F9" si="2">SUM(C8*D8)</f>
+        <v>34.0336</v>
+      </c>
+      <c r="G8" s="3">
+        <f>SUM(C8*E8)</f>
+        <v>23.900000000000002</v>
+      </c>
+      <c r="H8" s="3">
+        <f t="shared" si="1"/>
+        <v>467.8664</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="2">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" s="3">
+        <v>658</v>
+      </c>
+      <c r="D9" s="4">
+        <v>5.9900000000000002E-2</v>
+      </c>
+      <c r="E9" s="5">
+        <v>0.04</v>
+      </c>
+      <c r="F9" s="3">
         <f t="shared" si="2"/>
-        <v>443.96160000000003</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="2">
-        <v>500</v>
-      </c>
-      <c r="D5" s="1">
-        <v>8.6400000000000005E-2</v>
-      </c>
-      <c r="E5" s="1">
-        <v>0.06</v>
-      </c>
-      <c r="F5" s="3">
+        <v>39.414200000000001</v>
+      </c>
+      <c r="G9" s="3">
         <f t="shared" si="0"/>
-        <v>43.2</v>
-      </c>
-      <c r="G5" s="3">
-        <f t="shared" si="1"/>
-        <v>30</v>
-      </c>
-      <c r="H5" s="3">
-        <f t="shared" si="2"/>
-        <v>486.8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="2">
-        <v>850</v>
-      </c>
-      <c r="D6" s="1">
-        <v>8.9899999999999994E-2</v>
-      </c>
-      <c r="E6" s="1">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="F6" s="3">
-        <f t="shared" si="0"/>
-        <v>76.414999999999992</v>
-      </c>
-      <c r="G6" s="3">
-        <f t="shared" si="1"/>
-        <v>59.500000000000007</v>
-      </c>
-      <c r="H6" s="3">
-        <f t="shared" si="2"/>
-        <v>833.08500000000004</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" s="2">
-        <v>459</v>
-      </c>
-      <c r="D7" s="1">
-        <v>6.25E-2</v>
-      </c>
-      <c r="E7" s="1">
-        <v>0.05</v>
-      </c>
-      <c r="F7" s="3">
-        <f t="shared" si="0"/>
-        <v>28.6875</v>
-      </c>
-      <c r="G7" s="3">
-        <f t="shared" si="1"/>
-        <v>22.950000000000003</v>
-      </c>
-      <c r="H7" s="3">
-        <f t="shared" si="2"/>
-        <v>453.26249999999999</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C8" s="2">
-        <v>478</v>
-      </c>
-      <c r="D8" s="1">
-        <v>7.1199999999999999E-2</v>
-      </c>
-      <c r="E8" s="1">
-        <v>0.05</v>
-      </c>
-      <c r="F8" s="3">
-        <f t="shared" si="0"/>
-        <v>34.0336</v>
-      </c>
-      <c r="G8" s="3">
-        <f t="shared" si="1"/>
-        <v>23.900000000000002</v>
-      </c>
-      <c r="H8" s="3">
-        <f t="shared" si="2"/>
-        <v>467.8664</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9" t="s">
-        <v>15</v>
-      </c>
-      <c r="C9" s="2">
-        <v>658</v>
-      </c>
-      <c r="D9" s="1">
-        <v>5.9900000000000002E-2</v>
-      </c>
-      <c r="E9" s="1">
-        <v>0.04</v>
-      </c>
-      <c r="F9" s="3">
-        <f t="shared" si="0"/>
-        <v>39.414200000000001</v>
-      </c>
-      <c r="G9" s="3">
-        <f t="shared" si="1"/>
         <v>26.32</v>
       </c>
       <c r="H9" s="3">
-        <f t="shared" si="2"/>
+        <f>SUM(C9+G9-F9)</f>
         <v>644.9058</v>
       </c>
     </row>
